--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:09</t>
+    <t xml:space="preserve">2026-09-10 01:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:22</t>
+    <t xml:space="preserve">2026-09-12 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:34</t>
+    <t xml:space="preserve">2026-09-24 00:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
